--- a/kullanici_girisleri.xlsx
+++ b/kullanici_girisleri.xlsx
@@ -586,7 +586,7 @@
     <row r="2" ht="26" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>13.10.2026 16:50:10</t>
+          <t>01.11.2026 14:51:41</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
@@ -634,7 +634,7 @@
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>13.10.2026 16:50:10</t>
+          <t>01.11.2026 14:51:41</t>
         </is>
       </c>
       <c r="L2" s="2" t="inlineStr">
@@ -646,7 +646,7 @@
     <row r="3" ht="26" customHeight="1">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>13.10.2026 16:50:11</t>
+          <t>01.11.2026 14:51:41</t>
         </is>
       </c>
       <c r="B3" s="6" t="inlineStr">
@@ -694,7 +694,7 @@
       </c>
       <c r="K3" s="5" t="inlineStr">
         <is>
-          <t>13.10.2026 16:50:11</t>
+          <t>01.11.2026 14:51:41</t>
         </is>
       </c>
       <c r="L3" s="5" t="inlineStr">
@@ -706,7 +706,7 @@
     <row r="4" ht="26" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>13.10.2026 16:50:10</t>
+          <t>01.11.2026 14:51:41</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -754,7 +754,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>13.10.2026 16:50:10</t>
+          <t>01.11.2026 14:51:41</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
@@ -766,7 +766,7 @@
     <row r="5" ht="26" customHeight="1">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>13.10.2026 16:50:11</t>
+          <t>01.11.2026 14:51:42</t>
         </is>
       </c>
       <c r="B5" s="6" t="inlineStr">
@@ -814,7 +814,7 @@
       </c>
       <c r="K5" s="5" t="inlineStr">
         <is>
-          <t>13.10.2026 16:50:11</t>
+          <t>01.11.2026 14:51:42</t>
         </is>
       </c>
       <c r="L5" s="5" t="inlineStr">
@@ -910,7 +910,7 @@
     <row r="2" ht="24" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>13.10.2026 16:50:10</t>
+          <t>01.11.2026 14:51:41</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
@@ -965,7 +965,7 @@
     <row r="3" ht="24" customHeight="1">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>13.10.2026 16:50:10</t>
+          <t>01.11.2026 14:51:41</t>
         </is>
       </c>
       <c r="B3" s="6" t="inlineStr">
@@ -1020,7 +1020,7 @@
     <row r="4" ht="24" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>13.10.2026 16:50:11</t>
+          <t>01.11.2026 14:51:41</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -1075,7 +1075,7 @@
     <row r="5" ht="24" customHeight="1">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>13.10.2026 16:50:11</t>
+          <t>01.11.2026 14:51:42</t>
         </is>
       </c>
       <c r="B5" s="6" t="inlineStr">
@@ -1227,7 +1227,7 @@
     <row r="3" ht="42" customHeight="1">
       <c r="A3" s="8" t="inlineStr">
         <is>
-          <t>ornek@kullanici.com</t>
+          <t>elif.demir@example.com</t>
         </is>
       </c>
       <c r="B3" s="8" t="inlineStr">
@@ -1241,265 +1241,6 @@
         </is>
       </c>
       <c r="D3" s="8" t="inlineStr">
-        <is>
-          <t>1. Temizleyici -&gt; 2. Nemlendirici -&gt; 3. Güneş Kremi (SPF)</t>
-        </is>
-      </c>
-      <c r="E3" s="8" t="inlineStr">
-        <is>
-          <t>1. Temizleyici -&gt; 2. Onarıcı Nemlendirici</t>
-        </is>
-      </c>
-      <c r="F3" s="8" t="inlineStr">
-        <is>
-          <t>🌿 Temel Bariyer Koruma &amp; Dinlenme</t>
-        </is>
-      </c>
-      <c r="G3" s="8" t="inlineStr">
-        <is>
-          <t>Günlük koruma: Sabah SPF'i tazeleyin, akşam nazikçe temizleyip nemlendirin.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="42" customHeight="1">
-      <c r="A4" s="8" t="inlineStr">
-        <is>
-          <t>ornek@kullanici.com</t>
-        </is>
-      </c>
-      <c r="B4" s="8" t="inlineStr">
-        <is>
-          <t>Salı</t>
-        </is>
-      </c>
-      <c r="C4" s="8" t="inlineStr">
-        <is>
-          <t>Günün Bakımı</t>
-        </is>
-      </c>
-      <c r="D4" s="8" t="inlineStr">
-        <is>
-          <t>1. Temizleyici -&gt; 2. Nemlendirici -&gt; 3. Güneş Kremi (SPF)</t>
-        </is>
-      </c>
-      <c r="E4" s="8" t="inlineStr">
-        <is>
-          <t>1. Temizleyici -&gt; 2. Onarıcı Nemlendirici</t>
-        </is>
-      </c>
-      <c r="F4" s="8" t="inlineStr">
-        <is>
-          <t>🌿 Temel Bariyer Koruma &amp; Dinlenme</t>
-        </is>
-      </c>
-      <c r="G4" s="8" t="inlineStr">
-        <is>
-          <t>Günlük koruma: Sabah SPF'i tazeleyin, akşam nazikçe temizleyip nemlendirin.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="42" customHeight="1">
-      <c r="A5" s="8" t="inlineStr">
-        <is>
-          <t>ornek@kullanici.com</t>
-        </is>
-      </c>
-      <c r="B5" s="8" t="inlineStr">
-        <is>
-          <t>Çarşamba</t>
-        </is>
-      </c>
-      <c r="C5" s="8" t="inlineStr">
-        <is>
-          <t>Günün Bakımı</t>
-        </is>
-      </c>
-      <c r="D5" s="8" t="inlineStr">
-        <is>
-          <t>1. Temizleyici -&gt; 2. Nemlendirici -&gt; 3. Güneş Kremi (SPF)</t>
-        </is>
-      </c>
-      <c r="E5" s="8" t="inlineStr">
-        <is>
-          <t>1. Temizleyici -&gt; 2. Onarıcı Nemlendirici</t>
-        </is>
-      </c>
-      <c r="F5" s="8" t="inlineStr">
-        <is>
-          <t>🧪 Peeling / Asit Bakımı (Ölü Deri &amp; Gözenek)</t>
-        </is>
-      </c>
-      <c r="G5" s="8" t="inlineStr">
-        <is>
-          <t>Eksfoliasyon: Asit sonrası retinol kullanmayın, ertesi sabah mutlaka SPF sürün.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="42" customHeight="1">
-      <c r="A6" s="8" t="inlineStr">
-        <is>
-          <t>ornek@kullanici.com</t>
-        </is>
-      </c>
-      <c r="B6" s="8" t="inlineStr">
-        <is>
-          <t>Perşembe</t>
-        </is>
-      </c>
-      <c r="C6" s="8" t="inlineStr">
-        <is>
-          <t>Günün Bakımı</t>
-        </is>
-      </c>
-      <c r="D6" s="8" t="inlineStr">
-        <is>
-          <t>1. Temizleyici -&gt; 2. Nemlendirici -&gt; 3. Güneş Kremi (SPF)</t>
-        </is>
-      </c>
-      <c r="E6" s="8" t="inlineStr">
-        <is>
-          <t>1. Temizleyici -&gt; 2. Onarıcı Nemlendirici</t>
-        </is>
-      </c>
-      <c r="F6" s="8" t="inlineStr">
-        <is>
-          <t>🌿 Temel Bariyer Koruma &amp; Dinlenme</t>
-        </is>
-      </c>
-      <c r="G6" s="8" t="inlineStr">
-        <is>
-          <t>Günlük koruma: Sabah SPF'i tazeleyin, akşam nazikçe temizleyip nemlendirin.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="42" customHeight="1">
-      <c r="A7" s="8" t="inlineStr">
-        <is>
-          <t>ornek@kullanici.com</t>
-        </is>
-      </c>
-      <c r="B7" s="8" t="inlineStr">
-        <is>
-          <t>Cuma</t>
-        </is>
-      </c>
-      <c r="C7" s="8" t="inlineStr">
-        <is>
-          <t>Günün Bakımı</t>
-        </is>
-      </c>
-      <c r="D7" s="8" t="inlineStr">
-        <is>
-          <t>1. Temizleyici -&gt; 2. Nemlendirici -&gt; 3. Güneş Kremi (SPF)</t>
-        </is>
-      </c>
-      <c r="E7" s="8" t="inlineStr">
-        <is>
-          <t>1. Temizleyici -&gt; 2. Onarıcı Nemlendirici</t>
-        </is>
-      </c>
-      <c r="F7" s="8" t="inlineStr">
-        <is>
-          <t>🌿 Temel Bariyer Koruma &amp; Dinlenme</t>
-        </is>
-      </c>
-      <c r="G7" s="8" t="inlineStr">
-        <is>
-          <t>Günlük koruma: Sabah SPF'i tazeleyin, akşam nazikçe temizleyip nemlendirin.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="42" customHeight="1">
-      <c r="A8" s="8" t="inlineStr">
-        <is>
-          <t>ornek@kullanici.com</t>
-        </is>
-      </c>
-      <c r="B8" s="8" t="inlineStr">
-        <is>
-          <t>Cumartesi</t>
-        </is>
-      </c>
-      <c r="C8" s="8" t="inlineStr">
-        <is>
-          <t>Günün Bakımı</t>
-        </is>
-      </c>
-      <c r="D8" s="8" t="inlineStr">
-        <is>
-          <t>1. Temizleyici -&gt; 2. Nemlendirici -&gt; 3. Güneş Kremi (SPF)</t>
-        </is>
-      </c>
-      <c r="E8" s="8" t="inlineStr">
-        <is>
-          <t>1. Temizleyici -&gt; 2. Onarıcı Nemlendirici</t>
-        </is>
-      </c>
-      <c r="F8" s="8" t="inlineStr">
-        <is>
-          <t>🌿 Temel Bariyer Koruma &amp; Dinlenme</t>
-        </is>
-      </c>
-      <c r="G8" s="8" t="inlineStr">
-        <is>
-          <t>Günlük koruma: Sabah SPF'i tazeleyin, akşam nazikçe temizleyip nemlendirin.</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="42" customHeight="1">
-      <c r="A9" s="8" t="inlineStr">
-        <is>
-          <t>ornek@kullanici.com</t>
-        </is>
-      </c>
-      <c r="B9" s="8" t="inlineStr">
-        <is>
-          <t>Pazar</t>
-        </is>
-      </c>
-      <c r="C9" s="8" t="inlineStr">
-        <is>
-          <t>Günün Bakımı</t>
-        </is>
-      </c>
-      <c r="D9" s="8" t="inlineStr">
-        <is>
-          <t>1. Temizleyici -&gt; 2. Nemlendirici -&gt; 3. Güneş Kremi (SPF)</t>
-        </is>
-      </c>
-      <c r="E9" s="8" t="inlineStr">
-        <is>
-          <t>1. Temizleyici -&gt; 2. Onarıcı Nemlendirici</t>
-        </is>
-      </c>
-      <c r="F9" s="8" t="inlineStr">
-        <is>
-          <t>🧖‍♀️ Yoğun Nem &amp; Onarım Maskesi</t>
-        </is>
-      </c>
-      <c r="G9" s="8" t="inlineStr">
-        <is>
-          <t>Haftalık dinlenme: Maskeyi 15-20 dk uygulayın, cildin nem deposunu doldurun.</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="42" customHeight="1">
-      <c r="A10" s="8" t="inlineStr">
-        <is>
-          <t>elif.demir@example.com</t>
-        </is>
-      </c>
-      <c r="B10" s="8" t="inlineStr">
-        <is>
-          <t>Pazartesi</t>
-        </is>
-      </c>
-      <c r="C10" s="8" t="inlineStr">
-        <is>
-          <t>Günün Bakımı</t>
-        </is>
-      </c>
-      <c r="D10" s="8" t="inlineStr">
         <is>
           <t>1. 🧴 Temizleyici (CeraVe Foaming Cleanser)
 2. ✨ Niasinamid Serumu (The Ordinary Niacinamide 10%)
@@ -1507,254 +1248,513 @@
 4. ☀️ Güneş Kremi (Beauty of Joseon Relief Sun SPF50+)</t>
         </is>
       </c>
-      <c r="E10" s="8" t="inlineStr">
+      <c r="E3" s="8" t="inlineStr">
         <is>
           <t>1. 🧴 Temizleyici (CeraVe Foaming Cleanser)
 2. 🧊 Nemlendirici (La Roche-Posay Effaclar Duo+M)</t>
         </is>
       </c>
-      <c r="F10" s="8" t="inlineStr">
+      <c r="F3" s="8" t="inlineStr">
         <is>
           <t>🌿 Temel Bariyer Koruma &amp; Dinlenme</t>
         </is>
       </c>
-      <c r="G10" s="8" t="inlineStr">
+      <c r="G3" s="8" t="inlineStr">
         <is>
           <t>Günlük koruma: Sabah SPF'i tazeleyin, akşam nazikçe temizleyip nemlendirin.</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="42" customHeight="1">
-      <c r="A11" s="8" t="inlineStr">
+    <row r="4" ht="42" customHeight="1">
+      <c r="A4" s="8" t="inlineStr">
         <is>
           <t>elif.demir@example.com</t>
         </is>
       </c>
-      <c r="B11" s="8" t="inlineStr">
+      <c r="B4" s="8" t="inlineStr">
         <is>
           <t>Salı</t>
         </is>
       </c>
-      <c r="C11" s="8" t="inlineStr">
+      <c r="C4" s="8" t="inlineStr">
         <is>
           <t>Günün Bakımı</t>
         </is>
       </c>
-      <c r="D11" s="8" t="inlineStr">
+      <c r="D4" s="8" t="inlineStr">
         <is>
           <t>1. 🧴 Temizleyici (CeraVe Foaming Cleanser)
 2. 🧊 Nemlendirici (La Roche-Posay Effaclar Duo+M)
 3. ☀️ Güneş Kremi (Beauty of Joseon SPF50+)</t>
         </is>
       </c>
-      <c r="E11" s="8" t="inlineStr">
+      <c r="E4" s="8" t="inlineStr">
         <is>
           <t>1. 🧴 Temizleyici (CeraVe Foaming Cleanser)
 2. 🔬 Retinol (Kiehls Retinol Serum)
 3. 🌙 Bariyer Onarıcı Gece Nemlendiricisi (La Roche-Posay)</t>
         </is>
       </c>
-      <c r="F11" s="8" t="inlineStr">
+      <c r="F4" s="8" t="inlineStr">
         <is>
           <t>🔬 Retinol Uygulaması (Hücre Yenileme)</t>
         </is>
       </c>
-      <c r="G11" s="8" t="inlineStr">
+      <c r="G4" s="8" t="inlineStr">
         <is>
           <t>Gece yenilenmesi: Retinolü kuru cilde uygulayın, sonrasında nemlendiriciyle bariyeri destekleyin.</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="42" customHeight="1">
-      <c r="A12" s="8" t="inlineStr">
+    <row r="5" ht="42" customHeight="1">
+      <c r="A5" s="8" t="inlineStr">
         <is>
           <t>elif.demir@example.com</t>
         </is>
       </c>
-      <c r="B12" s="8" t="inlineStr">
+      <c r="B5" s="8" t="inlineStr">
         <is>
           <t>Çarşamba</t>
         </is>
       </c>
-      <c r="C12" s="8" t="inlineStr">
+      <c r="C5" s="8" t="inlineStr">
         <is>
           <t>Günün Bakımı</t>
         </is>
       </c>
-      <c r="D12" s="8" t="inlineStr">
+      <c r="D5" s="8" t="inlineStr">
         <is>
           <t>1. 🧴 Temizleyici (CeraVe Foaming Cleanser)
 2. ☀️ Güneş Kremi (Beauty of Joseon SPF50+)</t>
         </is>
       </c>
-      <c r="E12" s="8" t="inlineStr">
+      <c r="E5" s="8" t="inlineStr">
         <is>
           <t>1. 🧴 Temizleyici (CeraVe Foaming Cleanser)
 2. 🧪 Salisilik Asit (BHA) (The Purest Solutions BHA Toner)
 3. 🌙 Nemlendirici (La Roche-Posay)</t>
         </is>
       </c>
-      <c r="F12" s="8" t="inlineStr">
+      <c r="F5" s="8" t="inlineStr">
         <is>
           <t>🧪 Peeling / Asit Bakımı (Ölü Deri &amp; Gözenek)</t>
         </is>
       </c>
-      <c r="G12" s="8" t="inlineStr">
+      <c r="G5" s="8" t="inlineStr">
         <is>
           <t>Eksfoliasyon: Asit sonrası retinol kullanmayın, ertesi sabah mutlaka SPF sürün.</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="42" customHeight="1">
-      <c r="A13" s="8" t="inlineStr">
+    <row r="6" ht="42" customHeight="1">
+      <c r="A6" s="8" t="inlineStr">
         <is>
           <t>elif.demir@example.com</t>
         </is>
       </c>
-      <c r="B13" s="8" t="inlineStr">
+      <c r="B6" s="8" t="inlineStr">
         <is>
           <t>Perşembe</t>
         </is>
       </c>
-      <c r="C13" s="8" t="inlineStr">
+      <c r="C6" s="8" t="inlineStr">
         <is>
           <t>Günün Bakımı</t>
         </is>
       </c>
-      <c r="D13" s="8" t="inlineStr">
+      <c r="D6" s="8" t="inlineStr">
         <is>
           <t>1. 🧴 Temizleyici (CeraVe Foaming Cleanser)
 2. 🧊 Nemlendirici (La Roche-Posay)
 3. ☀️ Güneş Kremi (Beauty of Joseon SPF50+)</t>
         </is>
       </c>
-      <c r="E13" s="8" t="inlineStr">
+      <c r="E6" s="8" t="inlineStr">
         <is>
           <t>1. 🧴 Temizleyici (CeraVe Foaming Cleanser)
 2. 🔬 Retinol (Kiehls Retinol Serum)
 3. 🌙 Nemlendirici (La Roche-Posay)</t>
         </is>
       </c>
-      <c r="F13" s="8" t="inlineStr">
+      <c r="F6" s="8" t="inlineStr">
         <is>
           <t>🔬 Retinol Uygulaması (Hücre Yenileme)</t>
         </is>
       </c>
-      <c r="G13" s="8" t="inlineStr">
+      <c r="G6" s="8" t="inlineStr">
         <is>
           <t>Gece yenilenmesi: Retinolü kuru cilde uygulayın, sonrasında nemlendiriciyle bariyeri destekleyin.</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="42" customHeight="1">
-      <c r="A14" s="8" t="inlineStr">
+    <row r="7" ht="42" customHeight="1">
+      <c r="A7" s="8" t="inlineStr">
         <is>
           <t>elif.demir@example.com</t>
         </is>
       </c>
-      <c r="B14" s="8" t="inlineStr">
+      <c r="B7" s="8" t="inlineStr">
         <is>
           <t>Cuma</t>
         </is>
       </c>
-      <c r="C14" s="8" t="inlineStr">
+      <c r="C7" s="8" t="inlineStr">
         <is>
           <t>Günün Bakımı</t>
         </is>
       </c>
-      <c r="D14" s="8" t="inlineStr">
+      <c r="D7" s="8" t="inlineStr">
         <is>
           <t>1. 🧴 Temizleyici (CeraVe Foaming Cleanser)
 2. 🧊 Nemlendirici (La Roche-Posay)
 3. ☀️ Güneş Kremi (Beauty of Joseon SPF50+)</t>
         </is>
       </c>
-      <c r="E14" s="8" t="inlineStr">
+      <c r="E7" s="8" t="inlineStr">
         <is>
           <t>1. 🧴 Temizleyici (CeraVe Foaming Cleanser)
 2. 🌙 Onarıcı Gece Bakımı (La Roche-Posay)</t>
         </is>
       </c>
-      <c r="F14" s="8" t="inlineStr">
+      <c r="F7" s="8" t="inlineStr">
         <is>
           <t>🌿 Temel Bariyer Koruma &amp; Dinlenme</t>
         </is>
       </c>
-      <c r="G14" s="8" t="inlineStr">
+      <c r="G7" s="8" t="inlineStr">
         <is>
           <t>Günlük koruma: Sabah SPF'i tazeleyin, akşam nazikçe temizleyip nemlendirin.</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="42" customHeight="1">
-      <c r="A15" s="8" t="inlineStr">
+    <row r="8" ht="42" customHeight="1">
+      <c r="A8" s="8" t="inlineStr">
         <is>
           <t>elif.demir@example.com</t>
         </is>
       </c>
-      <c r="B15" s="8" t="inlineStr">
+      <c r="B8" s="8" t="inlineStr">
         <is>
           <t>Cumartesi</t>
         </is>
       </c>
-      <c r="C15" s="8" t="inlineStr">
+      <c r="C8" s="8" t="inlineStr">
         <is>
           <t>Günün Bakımı</t>
         </is>
       </c>
-      <c r="D15" s="8" t="inlineStr">
+      <c r="D8" s="8" t="inlineStr">
         <is>
           <t>1. 🧴 Temizleyici (CeraVe Foaming Cleanser)
 2. 🧊 Nemlendirici (La Roche-Posay)
 3. ☀️ Güneş Kremi (Beauty of Joseon SPF50+)</t>
         </is>
       </c>
-      <c r="E15" s="8" t="inlineStr">
+      <c r="E8" s="8" t="inlineStr">
         <is>
           <t>1. 🧴 Temizleyici (CeraVe Foaming Cleanser)
 2. 🔬 Retinol (Kiehls Retinol Serum)
 3. 🌙 Nemlendirici (La Roche-Posay)</t>
         </is>
       </c>
-      <c r="F15" s="8" t="inlineStr">
+      <c r="F8" s="8" t="inlineStr">
         <is>
           <t>🔬 Retinol Uygulaması (Hücre Yenileme)</t>
         </is>
       </c>
-      <c r="G15" s="8" t="inlineStr">
+      <c r="G8" s="8" t="inlineStr">
         <is>
           <t>Gece yenilenmesi: Retinolü kuru cilde uygulayın, sonrasında nemlendiriciyle bariyeri destekleyin.</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="42" customHeight="1">
-      <c r="A16" s="8" t="inlineStr">
+    <row r="9" ht="42" customHeight="1">
+      <c r="A9" s="8" t="inlineStr">
         <is>
           <t>elif.demir@example.com</t>
         </is>
       </c>
-      <c r="B16" s="8" t="inlineStr">
+      <c r="B9" s="8" t="inlineStr">
         <is>
           <t>Pazar</t>
         </is>
       </c>
-      <c r="C16" s="8" t="inlineStr">
+      <c r="C9" s="8" t="inlineStr">
         <is>
           <t>Günün Bakımı</t>
         </is>
       </c>
-      <c r="D16" s="8" t="inlineStr">
+      <c r="D9" s="8" t="inlineStr">
         <is>
           <t>1. 🧴 Temizleyici (CeraVe Foaming Cleanser)
 2. 🧊 Nemlendirici (La Roche-Posay)
 3. ☀️ Güneş Kremi (Beauty of Joseon SPF50+)</t>
         </is>
       </c>
-      <c r="E16" s="8" t="inlineStr">
+      <c r="E9" s="8" t="inlineStr">
         <is>
           <t>1. 🧴 Temizleyici (CeraVe Foaming Cleanser)
 2. 🧖‍♀️ Yatıştırıcı Maske (Im From Mugwort Mask)
 3. 🌙 Bariyer Onarıcı Nemlendirici (La Roche-Posay)</t>
+        </is>
+      </c>
+      <c r="F9" s="8" t="inlineStr">
+        <is>
+          <t>🧖‍♀️ Yoğun Nem &amp; Onarım Maskesi</t>
+        </is>
+      </c>
+      <c r="G9" s="8" t="inlineStr">
+        <is>
+          <t>Haftalık dinlenme: Maskeyi 15-20 dk uygulayın, cildin nem deposunu doldurun.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="42" customHeight="1">
+      <c r="A10" s="8" t="inlineStr">
+        <is>
+          <t>ornek@kullanici.com</t>
+        </is>
+      </c>
+      <c r="B10" s="8" t="inlineStr">
+        <is>
+          <t>Pazartesi</t>
+        </is>
+      </c>
+      <c r="C10" s="8" t="inlineStr">
+        <is>
+          <t>Günün Bakımı</t>
+        </is>
+      </c>
+      <c r="D10" s="8" t="inlineStr">
+        <is>
+          <t>1. Temizleyici -&gt; 2. Nemlendirici -&gt; 3. Güneş Kremi (SPF)</t>
+        </is>
+      </c>
+      <c r="E10" s="8" t="inlineStr">
+        <is>
+          <t>1. Temizleyici -&gt; 2. Onarıcı Nemlendirici</t>
+        </is>
+      </c>
+      <c r="F10" s="8" t="inlineStr">
+        <is>
+          <t>🌿 Temel Bariyer Koruma &amp; Dinlenme</t>
+        </is>
+      </c>
+      <c r="G10" s="8" t="inlineStr">
+        <is>
+          <t>Günlük koruma: Sabah SPF'i tazeleyin, akşam nazikçe temizleyip nemlendirin.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="42" customHeight="1">
+      <c r="A11" s="8" t="inlineStr">
+        <is>
+          <t>ornek@kullanici.com</t>
+        </is>
+      </c>
+      <c r="B11" s="8" t="inlineStr">
+        <is>
+          <t>Salı</t>
+        </is>
+      </c>
+      <c r="C11" s="8" t="inlineStr">
+        <is>
+          <t>Günün Bakımı</t>
+        </is>
+      </c>
+      <c r="D11" s="8" t="inlineStr">
+        <is>
+          <t>1. Temizleyici -&gt; 2. Nemlendirici -&gt; 3. Güneş Kremi (SPF)</t>
+        </is>
+      </c>
+      <c r="E11" s="8" t="inlineStr">
+        <is>
+          <t>1. Temizleyici -&gt; 2. Onarıcı Nemlendirici</t>
+        </is>
+      </c>
+      <c r="F11" s="8" t="inlineStr">
+        <is>
+          <t>🌿 Temel Bariyer Koruma &amp; Dinlenme</t>
+        </is>
+      </c>
+      <c r="G11" s="8" t="inlineStr">
+        <is>
+          <t>Günlük koruma: Sabah SPF'i tazeleyin, akşam nazikçe temizleyip nemlendirin.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="42" customHeight="1">
+      <c r="A12" s="8" t="inlineStr">
+        <is>
+          <t>ornek@kullanici.com</t>
+        </is>
+      </c>
+      <c r="B12" s="8" t="inlineStr">
+        <is>
+          <t>Çarşamba</t>
+        </is>
+      </c>
+      <c r="C12" s="8" t="inlineStr">
+        <is>
+          <t>Günün Bakımı</t>
+        </is>
+      </c>
+      <c r="D12" s="8" t="inlineStr">
+        <is>
+          <t>1. Temizleyici -&gt; 2. Nemlendirici -&gt; 3. Güneş Kremi (SPF)</t>
+        </is>
+      </c>
+      <c r="E12" s="8" t="inlineStr">
+        <is>
+          <t>1. Temizleyici -&gt; 2. Onarıcı Nemlendirici</t>
+        </is>
+      </c>
+      <c r="F12" s="8" t="inlineStr">
+        <is>
+          <t>🧪 Peeling / Asit Bakımı (Ölü Deri &amp; Gözenek)</t>
+        </is>
+      </c>
+      <c r="G12" s="8" t="inlineStr">
+        <is>
+          <t>Eksfoliasyon: Asit sonrası retinol kullanmayın, ertesi sabah mutlaka SPF sürün.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="42" customHeight="1">
+      <c r="A13" s="8" t="inlineStr">
+        <is>
+          <t>ornek@kullanici.com</t>
+        </is>
+      </c>
+      <c r="B13" s="8" t="inlineStr">
+        <is>
+          <t>Perşembe</t>
+        </is>
+      </c>
+      <c r="C13" s="8" t="inlineStr">
+        <is>
+          <t>Günün Bakımı</t>
+        </is>
+      </c>
+      <c r="D13" s="8" t="inlineStr">
+        <is>
+          <t>1. Temizleyici -&gt; 2. Nemlendirici -&gt; 3. Güneş Kremi (SPF)</t>
+        </is>
+      </c>
+      <c r="E13" s="8" t="inlineStr">
+        <is>
+          <t>1. Temizleyici -&gt; 2. Onarıcı Nemlendirici</t>
+        </is>
+      </c>
+      <c r="F13" s="8" t="inlineStr">
+        <is>
+          <t>🌿 Temel Bariyer Koruma &amp; Dinlenme</t>
+        </is>
+      </c>
+      <c r="G13" s="8" t="inlineStr">
+        <is>
+          <t>Günlük koruma: Sabah SPF'i tazeleyin, akşam nazikçe temizleyip nemlendirin.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="42" customHeight="1">
+      <c r="A14" s="8" t="inlineStr">
+        <is>
+          <t>ornek@kullanici.com</t>
+        </is>
+      </c>
+      <c r="B14" s="8" t="inlineStr">
+        <is>
+          <t>Cuma</t>
+        </is>
+      </c>
+      <c r="C14" s="8" t="inlineStr">
+        <is>
+          <t>Günün Bakımı</t>
+        </is>
+      </c>
+      <c r="D14" s="8" t="inlineStr">
+        <is>
+          <t>1. Temizleyici -&gt; 2. Nemlendirici -&gt; 3. Güneş Kremi (SPF)</t>
+        </is>
+      </c>
+      <c r="E14" s="8" t="inlineStr">
+        <is>
+          <t>1. Temizleyici -&gt; 2. Onarıcı Nemlendirici</t>
+        </is>
+      </c>
+      <c r="F14" s="8" t="inlineStr">
+        <is>
+          <t>🌿 Temel Bariyer Koruma &amp; Dinlenme</t>
+        </is>
+      </c>
+      <c r="G14" s="8" t="inlineStr">
+        <is>
+          <t>Günlük koruma: Sabah SPF'i tazeleyin, akşam nazikçe temizleyip nemlendirin.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="42" customHeight="1">
+      <c r="A15" s="8" t="inlineStr">
+        <is>
+          <t>ornek@kullanici.com</t>
+        </is>
+      </c>
+      <c r="B15" s="8" t="inlineStr">
+        <is>
+          <t>Cumartesi</t>
+        </is>
+      </c>
+      <c r="C15" s="8" t="inlineStr">
+        <is>
+          <t>Günün Bakımı</t>
+        </is>
+      </c>
+      <c r="D15" s="8" t="inlineStr">
+        <is>
+          <t>1. Temizleyici -&gt; 2. Nemlendirici -&gt; 3. Güneş Kremi (SPF)</t>
+        </is>
+      </c>
+      <c r="E15" s="8" t="inlineStr">
+        <is>
+          <t>1. Temizleyici -&gt; 2. Onarıcı Nemlendirici</t>
+        </is>
+      </c>
+      <c r="F15" s="8" t="inlineStr">
+        <is>
+          <t>🌿 Temel Bariyer Koruma &amp; Dinlenme</t>
+        </is>
+      </c>
+      <c r="G15" s="8" t="inlineStr">
+        <is>
+          <t>Günlük koruma: Sabah SPF'i tazeleyin, akşam nazikçe temizleyip nemlendirin.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="42" customHeight="1">
+      <c r="A16" s="8" t="inlineStr">
+        <is>
+          <t>ornek@kullanici.com</t>
+        </is>
+      </c>
+      <c r="B16" s="8" t="inlineStr">
+        <is>
+          <t>Pazar</t>
+        </is>
+      </c>
+      <c r="C16" s="8" t="inlineStr">
+        <is>
+          <t>Günün Bakımı</t>
+        </is>
+      </c>
+      <c r="D16" s="8" t="inlineStr">
+        <is>
+          <t>1. Temizleyici -&gt; 2. Nemlendirici -&gt; 3. Güneş Kremi (SPF)</t>
+        </is>
+      </c>
+      <c r="E16" s="8" t="inlineStr">
+        <is>
+          <t>1. Temizleyici -&gt; 2. Onarıcı Nemlendirici</t>
         </is>
       </c>
       <c r="F16" s="8" t="inlineStr">
